--- a/data_tables/balance_skill_text.xlsx
+++ b/data_tables/balance_skill_text.xlsx
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Heals RES: 5x -&gt; 5.25 -&gt; 5.5 -&gt; 5.75 -&gt; 6 -&gt; 6.25 -&gt; 6.5 -&gt; 6.75 -&gt; 7 -&gt; 7x (L10)
+          <t>Heals RES: 5x -&gt; 5.25 -&gt; 5.5 -&gt; 5.75 -&gt; 6 -&gt; 6.25 -&gt; 6.5 -&gt; 6.75 -&gt; 7 -&gt; 7.25x (L10)
 Heal Cap: 200 (+40-60/Lv) -&gt; 600   |   TP Cost: 11 (+3-5/Lv) -&gt; 48   |   Speed: 1.35x</t>
         </is>
       </c>

--- a/data_tables/balance_skill_text.xlsx
+++ b/data_tables/balance_skill_text.xlsx
@@ -574,13 +574,13 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ATK: 252% (+4-10%/Lv) -&gt; 314%   |   Paralysis: 30% (+3-5%/Lv) -&gt; 64% (L10)
+          <t>ATK: 328% (+6-15%/Lv) -&gt; 421%   |   Paralysis: 30% (+3-5%/Lv) -&gt; 64% (L10)
 Turns: 5 (Lv1-4) -&gt; 6 (Lv5-8) -&gt; 7 (Lv9-10)  |  TP Cost: 24 -&gt; 48  |  Speed: 1.1x</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rows D041 - D080: power of Oracles' Action, life, speed</t>
+          <t>Rows D041 - D080: power of Oracles' Action (x1.5 more on 2026-10-16), life, speed</t>
         </is>
       </c>
     </row>
@@ -1116,12 +1116,12 @@
       <c r="E22" t="inlineStr">
         <is>
           <t>Number of dodges: 1 -&gt; 2 -&gt; 3 -&gt; 4 -&gt; 5 (L1-5 Max)   |   Chant: 0.75x
-Turns: 3 -&gt; 3 -&gt; 4 -&gt; 4 -&gt; 5   |   TP Cost: 17 -&gt; 20 -&gt; 24 -&gt; 28 -&gt; 33   |   Speed: 0.85x</t>
+Turns: 4 -&gt; 4 -&gt; 5 -&gt; 5 -&gt; 6   |   TP Cost: 17 -&gt; 20 -&gt; 24 -&gt; 28 -&gt; 33   |   Speed: 0.85x</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rows K001: the generated box fell back to "Number of dodges UP"</t>
+          <t>Rows K001, V016 - V020 (one more turn): the generated box fell back to "Number of dodges UP"</t>
         </is>
       </c>
     </row>

--- a/data_tables/balance_skill_text.xlsx
+++ b/data_tables/balance_skill_text.xlsx
@@ -1088,7 +1088,7 @@
       <c r="E21" t="inlineStr">
         <is>
           <t>Number of dodges: 3 -&gt; 4 -&gt; 5 (L1-3 Max)   |   Turns: 3 -&gt; 4 -&gt; 5
-TP Cost: 30 -&gt; 38 -&gt; 46   |   Speed: 0.85x   |   Chant: 0.75x -&gt; 0.65x</t>
+TP Cost: 15 -&gt; 19 -&gt; 23   |   Speed: 0.85x   |   Chant: 1.2x -&gt; 1.12x -&gt; 1.04x</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">

--- a/data_tables/balance_skill_text.xlsx
+++ b/data_tables/balance_skill_text.xlsx
@@ -687,12 +687,12 @@
       <c r="E7" t="inlineStr">
         <is>
           <t>Max HP damage: 6% -&gt; 7% -&gt; 9% -&gt; 10% -&gt; 12% (L1-5 Max)   |   Accuracy: 64% (+4%/Lv)
-ATK: -6% -&gt; -12% (3 Turns) | Damage cap: 250 -&gt; 500 | TP Cost: 20 (+2-3/Lv) -&gt; 30</t>
+ATK: -6% -&gt; -12% (3 Turns) | Damage cap: 750 -&gt; 1500 | TP Cost: 20 (+2-3/Lv) -&gt; 30</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rows C068, A139, X001</t>
+          <t>Rows C068, A139, X001, K124-K157</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       <c r="E8" t="inlineStr">
         <is>
           <t>Max HP damage: 6% -&gt; 7% -&gt; 9% -&gt; 10% -&gt; 12% (L1-5 Max)   |   Accuracy: 64% (+4%/Lv)
-Evasion: -10% -&gt; -23% (3 Turns) | Damage cap: 250 -&gt; 500 | TP Cost: 20 (+2-3/Lv) -&gt; 30</t>
+Evasion: -10% -&gt; -23% (3 Turns) | Damage cap: 750 -&gt; 1500 | TP Cost: 20 (+2-3/Lv) -&gt; 30</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rows C165, A149, X011</t>
+          <t>Rows C165, A149, X011, K124-K157</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       <c r="E9" t="inlineStr">
         <is>
           <t>Max HP damage: 6% -&gt; 7% -&gt; 9% -&gt; 10% -&gt; 12% (L1-5 Max)   |   Accuracy: 64% (+4%/Lv)
-DEF: -6% -&gt; -12% (3 Turns) | Damage cap: 250 -&gt; 500 | TP Cost: 20 (+2-3/Lv) -&gt; 30</t>
+DEF: -15% -&gt; -30% (3 Turns) | Damage cap: 750 -&gt; 1500 | TP Cost: 20 (+2-3/Lv) -&gt; 30</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rows C064, A154, X016</t>
+          <t>Rows C064, A154, X016, K124-K157</t>
         </is>
       </c>
     </row>

--- a/data_tables/balance_skill_text.xlsx
+++ b/data_tables/balance_skill_text.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1185,6 +1185,93 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>TechniqueSkillData_0035.bin</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Aim</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Increase own accuracy and critical rate.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Accuracy: +15% (+1-2%/Lv) -&gt; +30%   |   Critical rate: +3% (+3%/Lv) -&gt; +30% (L10)
+Turns: 5 -&gt; 9   |   TP Cost: 5 (+2-3/Lv) -&gt; 28</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Row Y022: effect 31 added, 3 points of critical rate a level</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>MagicSkillData_0197.bin</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Accelerator</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Raise the party's speed.</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Rows V006 - V015, Y020: all allies, 27% - 40%, 8 turns</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>MagicSkillData_0198.bin</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Amplify</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Raise the party's max HP.</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Row Y021: all allies</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_tables/balance_skill_text.xlsx
+++ b/data_tables/balance_skill_text.xlsx
@@ -1203,18 +1203,18 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Increase own accuracy and critical rate.</t>
+          <t>Increase own accuracy and physical damage.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Accuracy: +15% (+1-2%/Lv) -&gt; +30%   |   Critical rate: +3% (+3%/Lv) -&gt; +30% (L10)
+          <t>Accuracy: +15% (+1-2%/Lv) -&gt; +30%   |   Damage: +10% (+2-3%/Lv) -&gt; +30%
 Turns: 5 -&gt; 9   |   TP Cost: 5 (+2-3/Lv) -&gt; 28</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Row Y022: effect 31 added, 3 points of critical rate a level</t>
+          <t>Row Y022: effect 191 added, damage +10% to +30%</t>
         </is>
       </c>
     </row>

--- a/data_tables/balance_skill_text.xlsx
+++ b/data_tables/balance_skill_text.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1272,6 +1272,38 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>PassiveSkillData_0244.bin</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Mace Mastery</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ATK and RES bonus with mace equipped.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>ATK and RES bonus: 5.6% -&gt; 9.4 -&gt; 13.1 -&gt; 16.9 -&gt; 18.8 -&gt; 20.6 -&gt; 22.5 -&gt; 24.4 -&gt; 26.3 -&gt; 28.1%</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Rows K114 - K123: the bonus reaches the RES of the mace as well (docs/FORMULAS.md 12.17)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_tables/balance_skill_text.xlsx
+++ b/data_tables/balance_skill_text.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1295,12 +1295,44 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>ATK and RES bonus: 5.6% -&gt; 9.4 -&gt; 13.1 -&gt; 16.9 -&gt; 18.8 -&gt; 20.6 -&gt; 22.5 -&gt; 24.4 -&gt; 26.3 -&gt; 28.1%</t>
+          <t>ATK/RES: 5.6% -&gt; 9.4 -&gt; 13.1 -&gt; 16.9 -&gt; 18.8 -&gt; 20.6 -&gt; 22.5 -&gt; 24.4 -&gt; 26.3 -&gt; 28.1%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
           <t>Rows K114 - K123: the bonus reaches the RES of the mace as well (docs/FORMULAS.md 12.17)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>PassiveSkillData_0264.bin</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Knock Down</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Occasionally parry and counterattack hits of any range.</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Activation rate: 18.8% -&gt; 28.1 -&gt; 37.5 -&gt; 46.9 -&gt; 56.2%</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Rows K056 - K060, Y023: rates x1.875 of vanilla, effect 250 added</t>
         </is>
       </c>
     </row>

--- a/data_tables/balance_skill_text.xlsx
+++ b/data_tables/balance_skill_text.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1336,6 +1336,39 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>TechniqueSkillData_0091.bin</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Life Bringer</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Short-range. Damage by enemy max HP and reduce its max HP.</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Max HP damage: 8% -&gt; 10% -&gt; 12% -&gt; 14% -&gt; 16% (L1-5 Max)   |   ATK: 110% -&gt; 150%
+Max HP reduction: 50% -&gt; 100%   |   TP Cost: 15 -&gt; 25   |   Speed: 0.85x</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Row Y024: effect 138 added; rows X056 - X060: ATK 110% to 150%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_tables/balance_skill_text.xlsx
+++ b/data_tables/balance_skill_text.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1369,6 +1369,39 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>MagicSkillData_0194.bin</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Protect</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Shield skill. Raise an ally's DEF and cut physical damage.</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>DEF: +20% -&gt; +28 -&gt; +36 -&gt; +44 -&gt; +50%   |   Damage reduction: 15% -&gt; 19 -&gt; 23 -&gt; 27 -&gt; 30%
+Turns: 5 -&gt; 9   |   TP Cost: 9 -&gt; 17   |   Speed: 2x -&gt; 2.25x   |   Chant: 3x</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Rows X066 - X070, Y025 - Y035: effect 179 added, quick cast</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
